--- a/slab_detailer/improtntinos3_output/improtntinos3_bar_schedule.xlsx
+++ b/slab_detailer/improtntinos3_output/improtntinos3_bar_schedule.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -559,7 +559,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1ф12x88/20</t>
+          <t>1Φ12x88/20</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1ф12x100/20</t>
+          <t>1Φ12x100/20</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3ф12x110/20</t>
+          <t>3Φ12x110/20</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6ф12x112/20</t>
+          <t>6Φ12x112/20</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5ф12x112/20</t>
+          <t>5Φ12x112/20</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12ф12x122/20</t>
+          <t>12Φ12x122/20</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2ф12x160/20</t>
+          <t>2Φ12x160/20</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26ф12x210/20</t>
+          <t>26Φ12x210/20</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9ф12x212/20</t>
+          <t>9Φ12x212/20</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4ф12x218/20</t>
+          <t>4Φ12x218/20</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4ф12x219/20</t>
+          <t>4Φ12x219/20</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4ф12x219/20</t>
+          <t>4Φ12x219/20</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2200</v>
+        <v>2260</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="I14" s="2">
         <f>G14*H14/1000</f>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3ф12x220/20</t>
+          <t>26Φ12x226/20</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1213,14 +1213,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2260</v>
+        <v>2640</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I15" s="2">
         <f>G15*H15/1000</f>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>26ф12x226/20</t>
+          <t>4Φ12x(220÷396)/20</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4ф12x276/20</t>
+          <t>4Φ12x276/20</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>45ф12x282/20</t>
+          <t>45Φ12x282/20</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6ф12x336/20</t>
+          <t>6Φ12x336/20</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>69ф12x341/20</t>
+          <t>69Φ12x341/20</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>45ф12x341/20</t>
+          <t>45Φ12x341/20</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>34ф12x342/20</t>
+          <t>34Φ12x342/20</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>35ф12x344/20</t>
+          <t>35Φ12x344/20</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>11ф12x360/20</t>
+          <t>11Φ12x360/20</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1ф12x372/20</t>
+          <t>1Φ12x372/20</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3960</v>
+        <v>4060</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="I25" s="2">
         <f>G25*H25/1000</f>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1ф12x396/20</t>
+          <t>42Φ12x406/20</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1785,14 +1785,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4060</v>
+        <v>4450</v>
       </c>
       <c r="H26" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="I26" s="2">
         <f>G26*H26/1000</f>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>42ф12x406/20</t>
+          <t>10Φ12x(416÷474)/20</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4160</v>
+        <v>4460</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I27" s="2">
         <f>G27*H27/1000</f>
@@ -1859,14 +1859,14 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5ф12x416/20</t>
+          <t>9Φ12x446/20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>N24</t>
+          <t>N23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1896,7 +1896,7 @@
         <v>4460</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I28" s="2">
         <f>G28*H28/1000</f>
@@ -1911,14 +1911,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>9ф12x446/20</t>
+          <t>7Φ12x446/20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>N24</t>
+          <t>N23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7ф12x446/20</t>
+          <t>7Φ12x446/20</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4460</v>
+        <v>4540</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I30" s="2">
         <f>G30*H30/1000</f>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7ф12x446/20</t>
+          <t>22Φ12x454/20</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4540</v>
+        <v>4580</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I31" s="2">
         <f>G31*H31/1000</f>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2ф12x454/20</t>
+          <t>32Φ12x458/20</t>
         </is>
       </c>
     </row>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4540</v>
+        <v>4580</v>
       </c>
       <c r="H32" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I32" s="2">
         <f>G32*H32/1000</f>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>22ф12x454/20</t>
+          <t>29Φ12x458/20</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>4580</v>
+        <v>4660</v>
       </c>
       <c r="H33" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I33" s="2">
         <f>G33*H33/1000</f>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>32ф12x458/20</t>
+          <t>69Φ12x466/20</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>4580</v>
+        <v>4660</v>
       </c>
       <c r="H34" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I34" s="2">
         <f>G34*H34/1000</f>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>29ф12x458/20</t>
+          <t>38Φ12x466/20</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>4660</v>
+        <v>4740</v>
       </c>
       <c r="H35" t="n">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="I35" s="2">
         <f>G35*H35/1000</f>
@@ -2275,14 +2275,14 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>69ф12x466/20</t>
+          <t>34Φ12x474/20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>N27</t>
+          <t>N28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>4660</v>
+        <v>4780</v>
       </c>
       <c r="H36" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I36" s="2">
         <f>G36*H36/1000</f>
@@ -2327,14 +2327,14 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>38ф12x466/20</t>
+          <t>24Φ12x478/20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>N28</t>
+          <t>N29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>4740</v>
+        <v>4810</v>
       </c>
       <c r="H37" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I37" s="2">
         <f>G37*H37/1000</f>
@@ -2379,14 +2379,14 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>34ф12x474/20</t>
+          <t>8Φ12x481/20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>N28</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4740</v>
+        <v>5040</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="I38" s="2">
         <f>G38*H38/1000</f>
@@ -2431,14 +2431,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5ф12x474/20</t>
+          <t>47Φ12x504/20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>N29</t>
+          <t>N31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4780</v>
+        <v>5100</v>
       </c>
       <c r="H39" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I39" s="2">
         <f>G39*H39/1000</f>
@@ -2483,14 +2483,14 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>24ф12x478/20</t>
+          <t>6Φ12x510/20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4820</v>
+        <v>5100</v>
       </c>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I40" s="2">
         <f>G40*H40/1000</f>
@@ -2535,14 +2535,14 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>8ф12x482/20</t>
+          <t>3Φ12x510/20</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>N31</t>
+          <t>N32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>4990</v>
+        <v>5120</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I41" s="2">
         <f>G41*H41/1000</f>
@@ -2587,14 +2587,14 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1ф12x499/20</t>
+          <t>4Φ12x512/20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>N32</t>
+          <t>N33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>5040</v>
+        <v>5160</v>
       </c>
       <c r="H42" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="I42" s="2">
         <f>G42*H42/1000</f>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>47ф12x504/20</t>
+          <t>12Φ12x516/20</t>
         </is>
       </c>
     </row>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5100</v>
+        <v>5160</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I43" s="2">
         <f>G43*H43/1000</f>
@@ -2691,14 +2691,14 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6ф12x510/20</t>
+          <t>9Φ12x516/20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>N33</t>
+          <t>N34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>5100</v>
+        <v>5260</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I44" s="2">
         <f>G44*H44/1000</f>
@@ -2743,14 +2743,14 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>5ф12x510/20</t>
+          <t>11Φ12x526/20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>N33</t>
+          <t>N34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>5100</v>
+        <v>5260</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I45" s="2">
         <f>G45*H45/1000</f>
@@ -2795,14 +2795,14 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>3ф12x510/20</t>
+          <t>11Φ12x526/20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>N34</t>
+          <t>N35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2825,11 +2825,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>5120</v>
+        <v>5260</v>
       </c>
       <c r="H46" t="n">
         <v>4</v>
@@ -2847,14 +2847,14 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>4ф12x512/20</t>
+          <t>4Φ12x(499÷534)/20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>N35</t>
+          <t>N36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>5160</v>
+        <v>5380</v>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I47" s="2">
         <f>G47*H47/1000</f>
@@ -2899,14 +2899,14 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>12ф12x516/20</t>
+          <t>11Φ12x538/20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>N35</t>
+          <t>N37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2929,14 +2929,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>5160</v>
+        <v>5410</v>
       </c>
       <c r="H48" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I48" s="2">
         <f>G48*H48/1000</f>
@@ -2951,14 +2951,14 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>9ф12x516/20</t>
+          <t>6Φ12x(454÷584)/20</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>N36</t>
+          <t>N38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>5260</v>
+        <v>5460</v>
       </c>
       <c r="H49" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="I49" s="2">
         <f>G49*H49/1000</f>
@@ -3003,14 +3003,14 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>11ф12x526/20</t>
+          <t>35Φ12x546/20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>N36</t>
+          <t>N38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>5260</v>
+        <v>5460</v>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="I50" s="2">
         <f>G50*H50/1000</f>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>11ф12x526/20</t>
+          <t>34Φ12x546/20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>N37</t>
+          <t>N39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3085,14 +3085,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>5340</v>
+        <v>5500</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I51" s="2">
         <f>G51*H51/1000</f>
@@ -3107,14 +3107,14 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>3ф12x534/20</t>
+          <t>9Φ12x(510÷600)/20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>N38</t>
+          <t>N40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>5380</v>
+        <v>5520</v>
       </c>
       <c r="H52" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I52" s="2">
         <f>G52*H52/1000</f>
@@ -3159,14 +3159,14 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>11ф12x538/20</t>
+          <t>16Φ12x552/20</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>N39</t>
+          <t>N40</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>5460</v>
+        <v>5520</v>
       </c>
       <c r="H53" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I53" s="2">
         <f>G53*H53/1000</f>
@@ -3211,14 +3211,14 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>35ф12x546/20</t>
+          <t>2Φ12x552/1060</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>N39</t>
+          <t>N41</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>5460</v>
+        <v>5620</v>
       </c>
       <c r="H54" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="I54" s="2">
         <f>G54*H54/1000</f>
@@ -3263,14 +3263,14 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>34ф12x546/20</t>
+          <t>4Φ12x562/20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>N40</t>
+          <t>N42</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>5520</v>
+        <v>5720</v>
       </c>
       <c r="H55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I55" s="2">
         <f>G55*H55/1000</f>
@@ -3315,14 +3315,14 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>9ф12x552/20</t>
+          <t>3Φ12x572/20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>N40</t>
+          <t>N43</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>5520</v>
+        <v>5740</v>
       </c>
       <c r="H56" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="I56" s="2">
         <f>G56*H56/1000</f>
@@ -3367,14 +3367,14 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>7ф12x552/20</t>
+          <t>34Φ12x574/20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>N40</t>
+          <t>N43</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5520</v>
+        <v>5740</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I57" s="2">
         <f>G57*H57/1000</f>
@@ -3419,14 +3419,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1ф12x552/20</t>
+          <t>5Φ12x574/20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>N40</t>
+          <t>N44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>5520</v>
+        <v>5820</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I58" s="2">
         <f>G58*H58/1000</f>
@@ -3471,14 +3471,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1ф12x552/20</t>
+          <t>8Φ12x582/20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>N41</t>
+          <t>N45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>5620</v>
+        <v>5860</v>
       </c>
       <c r="H59" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="I59" s="2">
         <f>G59*H59/1000</f>
@@ -3523,14 +3523,14 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>4ф12x562/20</t>
+          <t>74Φ12x586/20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>N42</t>
+          <t>N45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>5720</v>
+        <v>5860</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I60" s="2">
         <f>G60*H60/1000</f>
@@ -3575,14 +3575,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>3ф12x572/20</t>
+          <t>37Φ12x586/20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>N43</t>
+          <t>N45</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>5740</v>
+        <v>5860</v>
       </c>
       <c r="H61" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I61" s="2">
         <f>G61*H61/1000</f>
@@ -3627,14 +3627,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>34ф12x574/20</t>
+          <t>12Φ12x586/20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>N43</t>
+          <t>N46</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>5740</v>
+        <v>5920</v>
       </c>
       <c r="H62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I62" s="2">
         <f>G62*H62/1000</f>
@@ -3679,14 +3679,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>5ф12x574/20</t>
+          <t>8Φ12x592/20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>N44</t>
+          <t>N47</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>5810</v>
+        <v>6000</v>
       </c>
       <c r="H63" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="I63" s="2">
         <f>G63*H63/1000</f>
@@ -3731,14 +3731,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>8ф12x581/20</t>
+          <t>35Φ12x600/20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>N45</t>
+          <t>N47</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>5840</v>
+        <v>6000</v>
       </c>
       <c r="H64" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="I64" s="2">
         <f>G64*H64/1000</f>
@@ -3783,14 +3783,14 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>4ф12x584/20</t>
+          <t>34Φ12x600/20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>N46</t>
+          <t>N47</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>5860</v>
+        <v>6000</v>
       </c>
       <c r="H65" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="I65" s="2">
         <f>G65*H65/1000</f>
@@ -3835,14 +3835,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>74ф12x586/20</t>
+          <t>8Φ12x600/20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>N46</t>
+          <t>N47</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>5860</v>
+        <v>6000</v>
       </c>
       <c r="H66" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="I66" s="2">
         <f>G66*H66/1000</f>
@@ -3887,14 +3887,14 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>37ф12x586/20</t>
+          <t>8Φ12x600/20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>N46</t>
+          <t>N48</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3921,17 +3921,17 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>5860</v>
+        <v>880</v>
       </c>
       <c r="H67" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I67" s="2">
         <f>G67*H67/1000</f>
         <v/>
       </c>
       <c r="J67" t="n">
-        <v>0.888</v>
+        <v>1.208</v>
       </c>
       <c r="K67" s="3">
         <f>I67*J67</f>
@@ -3939,14 +3939,14 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>12ф12x586/20</t>
+          <t>1Φ14x88/20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>N47</t>
+          <t>N49</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3973,17 +3973,17 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>5920</v>
+        <v>1000</v>
       </c>
       <c r="H68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I68" s="2">
         <f>G68*H68/1000</f>
         <v/>
       </c>
       <c r="J68" t="n">
-        <v>0.888</v>
+        <v>1.208</v>
       </c>
       <c r="K68" s="3">
         <f>I68*J68</f>
@@ -3991,14 +3991,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>8ф12x592/20</t>
+          <t>1Φ14x100/20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>N48</t>
+          <t>N50</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4025,17 +4025,17 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>6000</v>
+        <v>1600</v>
       </c>
       <c r="H69" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I69" s="2">
         <f>G69*H69/1000</f>
         <v/>
       </c>
       <c r="J69" t="n">
-        <v>0.888</v>
+        <v>1.208</v>
       </c>
       <c r="K69" s="3">
         <f>I69*J69</f>
@@ -4043,14 +4043,14 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>35ф12x600/20</t>
+          <t>2Φ14x160/20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>N48</t>
+          <t>N51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4077,17 +4077,17 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>6000</v>
+        <v>1740</v>
       </c>
       <c r="H70" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="I70" s="2">
         <f>G70*H70/1000</f>
         <v/>
       </c>
       <c r="J70" t="n">
-        <v>0.888</v>
+        <v>1.208</v>
       </c>
       <c r="K70" s="3">
         <f>I70*J70</f>
@@ -4095,14 +4095,14 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>34ф12x600/20</t>
+          <t>5Φ14x174/20</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>N48</t>
+          <t>N52</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4129,17 +4129,17 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>6000</v>
+        <v>2120</v>
       </c>
       <c r="H71" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I71" s="2">
         <f>G71*H71/1000</f>
         <v/>
       </c>
       <c r="J71" t="n">
-        <v>0.888</v>
+        <v>1.208</v>
       </c>
       <c r="K71" s="3">
         <f>I71*J71</f>
@@ -4147,14 +4147,14 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8ф12x600/20</t>
+          <t>22Φ14x212/20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>N48</t>
+          <t>N53</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4181,17 +4181,17 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>6000</v>
+        <v>2180</v>
       </c>
       <c r="H72" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I72" s="2">
         <f>G72*H72/1000</f>
         <v/>
       </c>
       <c r="J72" t="n">
-        <v>0.888</v>
+        <v>1.208</v>
       </c>
       <c r="K72" s="3">
         <f>I72*J72</f>
@@ -4199,14 +4199,14 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>8ф12x600/20</t>
+          <t>4Φ14x218/20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>N48</t>
+          <t>N54</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4216,16 +4216,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>6000</v>
+        <v>2190</v>
       </c>
       <c r="H73" t="n">
         <v>4</v>
@@ -4243,7 +4243,7 @@
         <v/>
       </c>
       <c r="J73" t="n">
-        <v>0.888</v>
+        <v>1.208</v>
       </c>
       <c r="K73" s="3">
         <f>I73*J73</f>
@@ -4251,14 +4251,14 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>4ф12x600/20</t>
+          <t>4Φ14x219/20</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>N49</t>
+          <t>N54</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>880</v>
+        <v>2190</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I74" s="2">
         <f>G74*H74/1000</f>
@@ -4303,14 +4303,14 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>1ф14x88/20</t>
+          <t>4Φ14x219/20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>N50</t>
+          <t>N55</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1000</v>
+        <v>2330</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I75" s="2">
         <f>G75*H75/1000</f>
@@ -4355,14 +4355,14 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>1ф14x100/20</t>
+          <t>11Φ14x233/20</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>N51</t>
+          <t>N55</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1600</v>
+        <v>2330</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I76" s="2">
         <f>G76*H76/1000</f>
@@ -4407,14 +4407,14 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2ф14x160/20</t>
+          <t>11Φ14x233/20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>N52</t>
+          <t>N56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1740</v>
+        <v>2380</v>
       </c>
       <c r="H77" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="I77" s="2">
         <f>G77*H77/1000</f>
@@ -4459,14 +4459,14 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>5ф14x174/20</t>
+          <t>32Φ14x238/20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>N53</t>
+          <t>N56</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2120</v>
+        <v>2380</v>
       </c>
       <c r="H78" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I78" s="2">
         <f>G78*H78/1000</f>
@@ -4511,14 +4511,14 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>22ф14x212/20</t>
+          <t>29Φ14x238/20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>N54</t>
+          <t>N57</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -4545,10 +4545,10 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>2180</v>
+        <v>2420</v>
       </c>
       <c r="H79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I79" s="2">
         <f>G79*H79/1000</f>
@@ -4563,14 +4563,14 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>4ф14x218/20</t>
+          <t>1Φ14x242/20</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>N55</t>
+          <t>N58</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>2190</v>
+        <v>2440</v>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I80" s="2">
         <f>G80*H80/1000</f>
@@ -4615,14 +4615,14 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>4ф14x219/20</t>
+          <t>7Φ14x244/20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>N55</t>
+          <t>N59</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2190</v>
+        <v>2500</v>
       </c>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I81" s="2">
         <f>G81*H81/1000</f>
@@ -4667,14 +4667,14 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>4ф14x219/20</t>
+          <t>11Φ14x250/20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>N56</t>
+          <t>N60</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I82" s="2">
         <f>G82*H82/1000</f>
@@ -4719,14 +4719,14 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>3ф14x220/20</t>
+          <t>9Φ14x(242÷334)/20</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>N57</t>
+          <t>N61</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2320</v>
+        <v>2820</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I83" s="2">
         <f>G83*H83/1000</f>
@@ -4771,14 +4771,14 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>3ф14x232/20</t>
+          <t>8Φ14x282/20</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>N58</t>
+          <t>N62</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4801,14 +4801,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>2330</v>
+        <v>2950</v>
       </c>
       <c r="H84" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I84" s="2">
         <f>G84*H84/1000</f>
@@ -4823,14 +4823,14 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>11ф14x233/20</t>
+          <t>8Φ14x(264÷314)/20</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>N58</t>
+          <t>N63</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2330</v>
+        <v>2980</v>
       </c>
       <c r="H85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I85" s="2">
         <f>G85*H85/1000</f>
@@ -4875,14 +4875,14 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>11ф14x233/20</t>
+          <t>12Φ14x298/20</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>N59</t>
+          <t>N63</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>2380</v>
+        <v>2980</v>
       </c>
       <c r="H86" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="I86" s="2">
         <f>G86*H86/1000</f>
@@ -4927,14 +4927,14 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>32ф14x238/20</t>
+          <t>9Φ14x298/20</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>N59</t>
+          <t>N64</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -4961,10 +4961,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2380</v>
+        <v>3040</v>
       </c>
       <c r="H87" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I87" s="2">
         <f>G87*H87/1000</f>
@@ -4979,14 +4979,14 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>29ф14x238/20</t>
+          <t>24Φ14x304/20</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>N60</t>
+          <t>N65</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5009,14 +5009,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>2420</v>
+        <v>3040</v>
       </c>
       <c r="H88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I88" s="2">
         <f>G88*H88/1000</f>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>6ф14x242/20</t>
+          <t>7Φ14x(244÷314)/20</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>N60</t>
+          <t>N66</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -5061,14 +5061,14 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>2420</v>
+        <v>3050</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I89" s="2">
         <f>G89*H89/1000</f>
@@ -5083,14 +5083,14 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>1ф14x242/20</t>
+          <t>4Φ14x(220÷562)/20</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>N61</t>
+          <t>N67</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>2440</v>
+        <v>3120</v>
       </c>
       <c r="H90" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I90" s="2">
         <f>G90*H90/1000</f>
@@ -5135,14 +5135,14 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>7ф14x244/20</t>
+          <t>3Φ14x312/20</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>N61</t>
+          <t>N68</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>2440</v>
+        <v>3160</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I91" s="2">
         <f>G91*H91/1000</f>
@@ -5187,14 +5187,14 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>1ф14x244/20</t>
+          <t>6Φ14x(232÷400)/20</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>N62</t>
+          <t>N69</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>2500</v>
+        <v>3180</v>
       </c>
       <c r="H92" t="n">
         <v>11</v>
@@ -5239,14 +5239,14 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>11ф14x250/20</t>
+          <t>11Φ14x318/20</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>N63</t>
+          <t>N70</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2640</v>
+        <v>3240</v>
       </c>
       <c r="H93" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I93" s="2">
         <f>G93*H93/1000</f>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>3ф14x264/20</t>
+          <t>12Φ14x324/20</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>N64</t>
+          <t>N71</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>2730</v>
+        <v>3910</v>
       </c>
       <c r="H94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I94" s="2">
         <f>G94*H94/1000</f>
@@ -5343,14 +5343,14 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>3ф14x(242÷334)/20</t>
+          <t>4Φ14x(340÷544)/20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>N65</t>
+          <t>N72</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2820</v>
+        <v>4120</v>
       </c>
       <c r="H95" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I95" s="2">
         <f>G95*H95/1000</f>
@@ -5395,14 +5395,14 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>8ф14x282/20</t>
+          <t>26Φ14x412/20</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>N66</t>
+          <t>N73</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>2980</v>
+        <v>4280</v>
       </c>
       <c r="H96" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="I96" s="2">
         <f>G96*H96/1000</f>
@@ -5447,14 +5447,14 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>12ф14x298/20</t>
+          <t>26Φ14x428/20</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>N66</t>
+          <t>N74</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>2980</v>
+        <v>4480</v>
       </c>
       <c r="H97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I97" s="2">
         <f>G97*H97/1000</f>
@@ -5499,14 +5499,14 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>9ф14x298/20</t>
+          <t>11Φ14x448/20</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>N67</t>
+          <t>N74</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>3040</v>
+        <v>4480</v>
       </c>
       <c r="H98" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I98" s="2">
         <f>G98*H98/1000</f>
@@ -5551,14 +5551,14 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>24ф14x304/20</t>
+          <t>11Φ14x448/20</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>N68</t>
+          <t>N75</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>3120</v>
+        <v>4500</v>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="I99" s="2">
         <f>G99*H99/1000</f>
@@ -5603,14 +5603,14 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>3ф14x312/20</t>
+          <t>73Φ14x450/20</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>N69</t>
+          <t>N76</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -5637,10 +5637,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>3140</v>
+        <v>4540</v>
       </c>
       <c r="H100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I100" s="2">
         <f>G100*H100/1000</f>
@@ -5655,14 +5655,14 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>6ф14x314/20</t>
+          <t>3Φ14x454/20</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>N69</t>
+          <t>N77</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>3140</v>
+        <v>4570</v>
       </c>
       <c r="H101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I101" s="2">
         <f>G101*H101/1000</f>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>5ф14x314/20</t>
+          <t>3Φ14x457/20</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>N70</t>
+          <t>N78</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>3180</v>
+        <v>4580</v>
       </c>
       <c r="H102" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I102" s="2">
         <f>G102*H102/1000</f>
@@ -5759,14 +5759,14 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>11ф14x318/20</t>
+          <t>8Φ14x458/20</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>N71</t>
+          <t>N79</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -5789,14 +5789,14 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3240</v>
+        <v>4690</v>
       </c>
       <c r="H103" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I103" s="2">
         <f>G103*H103/1000</f>
@@ -5811,14 +5811,14 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>12ф14x324/20</t>
+          <t>9Φ14x(418÷510)/20</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>N72</t>
+          <t>N80</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -5841,14 +5841,14 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>straight (variable, avg. length)</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3400</v>
+        <v>4740</v>
       </c>
       <c r="H104" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I104" s="2">
         <f>G104*H104/1000</f>
@@ -5863,14 +5863,14 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>3ф14x340/20</t>
+          <t>6Φ14x(454÷484)/20</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>N73</t>
+          <t>N81</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>4000</v>
+        <v>4800</v>
       </c>
       <c r="H105" t="n">
         <v>3</v>
@@ -5915,14 +5915,14 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>3ф14x400/20</t>
+          <t>3Φ14x480/20</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>N74</t>
+          <t>N82</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>4120</v>
+        <v>4840</v>
       </c>
       <c r="H106" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I106" s="2">
         <f>G106*H106/1000</f>
@@ -5967,14 +5967,14 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>26ф14x412/20</t>
+          <t>45Φ14x484/20</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>N75</t>
+          <t>N83</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>4180</v>
+        <v>4910</v>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="I107" s="2">
         <f>G107*H107/1000</f>
@@ -6019,14 +6019,14 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>4ф14x418/20</t>
+          <t>47Φ14x491/20</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>N76</t>
+          <t>N84</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>4280</v>
+        <v>5080</v>
       </c>
       <c r="H108" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I108" s="2">
         <f>G108*H108/1000</f>
@@ -6071,14 +6071,14 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>26ф14x428/20</t>
+          <t>8Φ14x508/20</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>N77</t>
+          <t>N85</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>4480</v>
+        <v>5100</v>
       </c>
       <c r="H109" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I109" s="2">
         <f>G109*H109/1000</f>
@@ -6123,14 +6123,14 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>11ф14x448/20</t>
+          <t>6Φ14x510/20</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>N77</t>
+          <t>N86</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>4480</v>
+        <v>5240</v>
       </c>
       <c r="H110" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="I110" s="2">
         <f>G110*H110/1000</f>
@@ -6175,14 +6175,14 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>11ф14x448/20</t>
+          <t>42Φ14x524/20</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>N78</t>
+          <t>N87</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6209,10 +6209,10 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>4500</v>
+        <v>5320</v>
       </c>
       <c r="H111" t="n">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="I111" s="2">
         <f>G111*H111/1000</f>
@@ -6227,14 +6227,14 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>73ф14x450/20</t>
+          <t>9Φ14x532/20</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>N79</t>
+          <t>N88</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>4540</v>
+        <v>5330</v>
       </c>
       <c r="H112" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="I112" s="2">
         <f>G112*H112/1000</f>
@@ -6279,14 +6279,14 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2ф14x454/20</t>
+          <t>72Φ14x533/20</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>N79</t>
+          <t>N89</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>4540</v>
+        <v>5360</v>
       </c>
       <c r="H113" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I113" s="2">
         <f>G113*H113/1000</f>
@@ -6331,14 +6331,14 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>3ф14x454/20</t>
+          <t>51Φ14x536/20</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>N80</t>
+          <t>N90</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>4570</v>
+        <v>5400</v>
       </c>
       <c r="H114" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I114" s="2">
         <f>G114*H114/1000</f>
@@ -6383,14 +6383,14 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>3ф14x457/20</t>
+          <t>9Φ14x540/20</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>N81</t>
+          <t>N90</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>4580</v>
+        <v>5400</v>
       </c>
       <c r="H115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I115" s="2">
         <f>G115*H115/1000</f>
@@ -6435,14 +6435,14 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>8ф14x458/20</t>
+          <t>7Φ14x540/20</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>N82</t>
+          <t>N90</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>4800</v>
+        <v>5400</v>
       </c>
       <c r="H116" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I116" s="2">
         <f>G116*H116/1000</f>
@@ -6487,14 +6487,14 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>3ф14x480/20</t>
+          <t>7Φ14x540/20</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>N83</t>
+          <t>N91</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>4840</v>
+        <v>5660</v>
       </c>
       <c r="H117" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="I117" s="2">
         <f>G117*H117/1000</f>
@@ -6539,14 +6539,14 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>45ф14x484/20</t>
+          <t>34Φ14x566/20</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>N83</t>
+          <t>N92</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>4840</v>
+        <v>5670</v>
       </c>
       <c r="H118" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I118" s="2">
         <f>G118*H118/1000</f>
@@ -6591,14 +6591,14 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>4ф14x484/20</t>
+          <t>35Φ14x567/20</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>N84</t>
+          <t>N93</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>4910</v>
+        <v>5770</v>
       </c>
       <c r="H119" t="n">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="I119" s="2">
         <f>G119*H119/1000</f>
@@ -6643,14 +6643,14 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>47ф14x491/20</t>
+          <t>104Φ14x577/20</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>N85</t>
+          <t>N93</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>5080</v>
+        <v>5770</v>
       </c>
       <c r="H120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I120" s="2">
         <f>G120*H120/1000</f>
@@ -6695,14 +6695,14 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>8ф14x508/20</t>
+          <t>9Φ14x577/20</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>N86</t>
+          <t>N93</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -6729,10 +6729,10 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>5100</v>
+        <v>5770</v>
       </c>
       <c r="H121" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I121" s="2">
         <f>G121*H121/1000</f>
@@ -6747,14 +6747,14 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>6ф14x510/20</t>
+          <t>7Φ14x577/20</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>N86</t>
+          <t>N94</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>5100</v>
+        <v>5840</v>
       </c>
       <c r="H122" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="I122" s="2">
         <f>G122*H122/1000</f>
@@ -6799,14 +6799,14 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>5ф14x510/20</t>
+          <t>38Φ14x584/20</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>N87</t>
+          <t>N95</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>5240</v>
+        <v>5950</v>
       </c>
       <c r="H123" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="I123" s="2">
         <f>G123*H123/1000</f>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>42ф14x524/20</t>
+          <t>74Φ14x595/20</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>N88</t>
+          <t>N96</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>5320</v>
+        <v>6000</v>
       </c>
       <c r="H124" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I124" s="2">
         <f>G124*H124/1000</f>
@@ -6903,14 +6903,14 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>9ф14x532/20</t>
+          <t>11Φ14x600/20</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>N89</t>
+          <t>N96</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -6937,10 +6937,10 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>5330</v>
+        <v>6000</v>
       </c>
       <c r="H125" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I125" s="2">
         <f>G125*H125/1000</f>
@@ -6955,14 +6955,14 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>72ф14x533/20</t>
+          <t>11Φ14x600/20</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>N90</t>
+          <t>N96</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>5360</v>
+        <v>6000</v>
       </c>
       <c r="H126" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="I126" s="2">
         <f>G126*H126/1000</f>
@@ -7007,14 +7007,14 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>51ф14x536/20</t>
+          <t>1Φ14x600/20</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>N91</t>
+          <t>N96</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="H127" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="I127" s="2">
         <f>G127*H127/1000</f>
@@ -7059,14 +7059,14 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>9ф14x540/20</t>
+          <t>35Φ14x600/20</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>N91</t>
+          <t>N96</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -7093,10 +7093,10 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="H128" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="I128" s="2">
         <f>G128*H128/1000</f>
@@ -7111,816 +7111,36 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>7ф14x540/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>N91</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>14</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>5400</v>
-      </c>
-      <c r="H129" t="n">
-        <v>7</v>
-      </c>
-      <c r="I129" s="2">
-        <f>G129*H129/1000</f>
-        <v/>
-      </c>
-      <c r="J129" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K129" s="3">
-        <f>I129*J129</f>
-        <v/>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>7ф14x540/20</t>
+          <t>34Φ14x600/20</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>N92</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>14</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>5440</v>
-      </c>
-      <c r="H130" t="n">
-        <v>1</v>
-      </c>
-      <c r="I130" s="2">
-        <f>G130*H130/1000</f>
-        <v/>
-      </c>
-      <c r="J130" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K130" s="3">
-        <f>I130*J130</f>
-        <v/>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>1ф14x544/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>N93</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
-        <v>14</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
-        <v>5620</v>
-      </c>
-      <c r="H131" t="n">
-        <v>1</v>
-      </c>
-      <c r="I131" s="2">
-        <f>G131*H131/1000</f>
-        <v/>
-      </c>
-      <c r="J131" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K131" s="3">
-        <f>I131*J131</f>
-        <v/>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>1ф14x562/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>N94</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>14</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G132" t="n">
-        <v>5660</v>
-      </c>
-      <c r="H132" t="n">
-        <v>34</v>
-      </c>
-      <c r="I132" s="2">
-        <f>G132*H132/1000</f>
-        <v/>
-      </c>
-      <c r="J132" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K132" s="3">
-        <f>I132*J132</f>
-        <v/>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>34ф14x566/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>N95</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>14</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
-        <v>5670</v>
-      </c>
-      <c r="H133" t="n">
-        <v>35</v>
-      </c>
-      <c r="I133" s="2">
-        <f>G133*H133/1000</f>
-        <v/>
-      </c>
-      <c r="J133" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K133" s="3">
-        <f>I133*J133</f>
-        <v/>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>35ф14x567/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>N96</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>14</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
-        <v>5770</v>
-      </c>
-      <c r="H134" t="n">
-        <v>104</v>
-      </c>
-      <c r="I134" s="2">
-        <f>G134*H134/1000</f>
-        <v/>
-      </c>
-      <c r="J134" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K134" s="3">
-        <f>I134*J134</f>
-        <v/>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>104ф14x577/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>N96</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
-        <v>14</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>5770</v>
-      </c>
-      <c r="H135" t="n">
-        <v>9</v>
-      </c>
-      <c r="I135" s="2">
-        <f>G135*H135/1000</f>
-        <v/>
-      </c>
-      <c r="J135" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K135" s="3">
-        <f>I135*J135</f>
-        <v/>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>9ф14x577/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>N96</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
-        <v>14</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>5770</v>
-      </c>
-      <c r="H136" t="n">
-        <v>7</v>
-      </c>
-      <c r="I136" s="2">
-        <f>G136*H136/1000</f>
-        <v/>
-      </c>
-      <c r="J136" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K136" s="3">
-        <f>I136*J136</f>
-        <v/>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>7ф14x577/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>N97</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>14</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>5840</v>
-      </c>
-      <c r="H137" t="n">
-        <v>38</v>
-      </c>
-      <c r="I137" s="2">
-        <f>G137*H137/1000</f>
-        <v/>
-      </c>
-      <c r="J137" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K137" s="3">
-        <f>I137*J137</f>
-        <v/>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>38ф14x584/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>N98</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>14</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>5950</v>
-      </c>
-      <c r="H138" t="n">
-        <v>74</v>
-      </c>
-      <c r="I138" s="2">
-        <f>G138*H138/1000</f>
-        <v/>
-      </c>
-      <c r="J138" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K138" s="3">
-        <f>I138*J138</f>
-        <v/>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>74ф14x595/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>N99</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>14</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H139" t="n">
-        <v>11</v>
-      </c>
-      <c r="I139" s="2">
-        <f>G139*H139/1000</f>
-        <v/>
-      </c>
-      <c r="J139" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K139" s="3">
-        <f>I139*J139</f>
-        <v/>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>11ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>N99</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>14</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H140" t="n">
-        <v>11</v>
-      </c>
-      <c r="I140" s="2">
-        <f>G140*H140/1000</f>
-        <v/>
-      </c>
-      <c r="J140" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K140" s="3">
-        <f>I140*J140</f>
-        <v/>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>11ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>N99</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>14</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H141" t="n">
-        <v>1</v>
-      </c>
-      <c r="I141" s="2">
-        <f>G141*H141/1000</f>
-        <v/>
-      </c>
-      <c r="J141" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K141" s="3">
-        <f>I141*J141</f>
-        <v/>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>1ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>N99</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>14</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H142" t="n">
-        <v>35</v>
-      </c>
-      <c r="I142" s="2">
-        <f>G142*H142/1000</f>
-        <v/>
-      </c>
-      <c r="J142" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K142" s="3">
-        <f>I142*J142</f>
-        <v/>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>35ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>N99</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>14</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G143" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H143" t="n">
-        <v>34</v>
-      </c>
-      <c r="I143" s="2">
-        <f>G143*H143/1000</f>
-        <v/>
-      </c>
-      <c r="J143" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K143" s="3">
-        <f>I143*J143</f>
-        <v/>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>34ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr"/>
-      <c r="C145" s="4" t="inlineStr"/>
-      <c r="D145" s="4" t="inlineStr"/>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
-      <c r="G145" s="4" t="inlineStr"/>
-      <c r="H145" s="4">
-        <f>SUM(H2:H143)</f>
-        <v/>
-      </c>
-      <c r="I145" s="4">
-        <f>SUM(I2:I143)</f>
-        <v/>
-      </c>
-      <c r="J145" s="4" t="inlineStr"/>
-      <c r="K145" s="4">
-        <f>SUM(K2:K143)</f>
-        <v/>
-      </c>
-      <c r="L145" s="4" t="n"/>
+      <c r="B130" s="4" t="inlineStr"/>
+      <c r="C130" s="4" t="inlineStr"/>
+      <c r="D130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
+      <c r="G130" s="4" t="inlineStr"/>
+      <c r="H130" s="4">
+        <f>SUM(H2:H128)</f>
+        <v/>
+      </c>
+      <c r="I130" s="4">
+        <f>SUM(I2:I128)</f>
+        <v/>
+      </c>
+      <c r="J130" s="4" t="inlineStr"/>
+      <c r="K130" s="4">
+        <f>SUM(K2:K128)</f>
+        <v/>
+      </c>
+      <c r="L130" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7969,7 +7189,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="3">
-        <f>SUMIF('Bar schedule'!E2:E143,A2,'Bar schedule'!I2:I143)</f>
+        <f>SUMIF('Bar schedule'!E2:E128,A2,'Bar schedule'!I2:I128)</f>
         <v/>
       </c>
       <c r="C2" t="n">
@@ -7985,7 +7205,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="3">
-        <f>SUMIF('Bar schedule'!E2:E143,A3,'Bar schedule'!I2:I143)</f>
+        <f>SUMIF('Bar schedule'!E2:E128,A3,'Bar schedule'!I2:I128)</f>
         <v/>
       </c>
       <c r="C3" t="n">
